--- a/docs/文章.xlsx
+++ b/docs/文章.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <r>
       <t>少年劍客林庭宇初出茅廬，聽聞「天劍門」廣招弟子，便背著木劍上山。山路陡峭，崖邊積雪未融，他走得如履薄冰，深怕一失足成千古恨。
@@ -152,6 +152,35 @@
   </si>
   <si>
     <t>文章</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>劍走凌霄：林庭宇的江湖道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>江湖風雲變幻，各大門派為了爭奪「天下第一劍」的虛名交戰不休。年輕劍客林庭宇雖身負絕世劍藝，卻因不屑名利，常年棲身於江南小鎮。
+早年，同門師兄常指責他終日彈琴吟詩是無病呻吟，但林庭宇從不妄自菲薄，更不曾陷入自怨自艾的頹喪中。他深知自己的劍法早已臻至化境，只是不願將自身武藝當作商品般待價而沽，投靠權貴罷了。
+當時的各大正派掌門皆奉朝廷與總壇之命行事，人人俯首貼耳，唯命是從。林庭宇看在眼裡，心中極為不齒，深感「寧為雞首，不為牛後」，絕不做他人的傀儡。
+某日，黑白兩道於楓林渡口決戰，形勢萬分危急。旁觀的江湖散人多持騎牆之見，只顧作壁上觀，甚至對受難百姓的哀嚎置若罔聞。林庭宇見狀怒不可遏，再也無法作罷。他秉持著劍及履及的豪情，當即拔劍而出，身形如雷霆般直奔戰場！
+眼見林庭宇一劍驚天，敵方首領自恃功力深厚、剛愎自用，根本不把眼前的小輩放在眼裡；然而其師心自用的自大，最終讓他落得慘敗的下場。
+一戰成名後，各大門派紛紛攜重金前來拉攏，許以高位。林庭宇只是冷笑一聲，隨即拂袖而去，重新踏入滾滾紅塵，只留下一段飄逸絕倫的俠義傳奇。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表現態度2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>清晨的陽光灑進客廳，林書聿坐在沙發上翻看著手機裡的職缺訊息。離職這幾個月來，身邊親友常覺得他整天發文抒發情緒不過是無病呻吟，但林書聿並未因此妄自菲薄，也未曾沉溺於自怨自艾的負面情緒中。他很清楚自己的專業實力，只是不想為了求職而輕易妥協，如商品般待價而沽，更不願再像過去那樣對上司俯首貼耳、唯命是從。
+「寧為雞首，不為牛後。」他在心裡默默重複這句座右銘。他渴望的是能獨當一面、掌握主導權的工作，而不是在大企業裡當個隨時能被替換的螺絲釘。
+中午，大學好友傳來訊息，邀請他加入一家剛起步的創業團隊。面對這個充滿未知與挑戰的選擇，身邊不少朋友抱持著騎牆之見，勸他先作壁上觀，甚至對創業團隊的願景置若罔聞。但林書聿不同，他向來講求效率與執行力，一旦認準方向便劍及履及，絕不拖泥帶水。
+前東家的主管曾因剛愎自用且師心自用，完全聽不進基層的建議，導致許多優秀的專案無疾而終，最終讓林書聿憤而拂袖而去。這段經驗讓他更加確定，自己要找的是一個能夠尊重專業、攜手並進的夥伴環境。
+合上手機，林書聿起走到陽台為綠植澆水。他深吸一口氣，決定下午就去和好友會面，正式開啟這段全新的職涯冒險。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陽台上的微光：林書聿的日常抉擇</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -423,11 +452,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="33.5703125" customWidth="1"/>
     <col min="3" max="3" width="255.7109375" customWidth="1"/>
     <col min="4" max="4" width="54.85546875" customWidth="1"/>
     <col min="5" max="5" width="81.7109375" customWidth="1"/>
@@ -471,6 +500,28 @@
         <v>5</v>
       </c>
     </row>
+    <row r="6" spans="1:3" ht="140.25">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="127.5">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/文章.xlsx
+++ b/docs/文章.xlsx
@@ -500,6 +500,7 @@
         <v>5</v>
       </c>
     </row>
+    <row r="5" spans="1:3" s="4" customFormat="1"/>
     <row r="6" spans="1:3" ht="140.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
